--- a/files/R01-R69全节点业务验收测试包/V00_R01-R69覆盖验证/V00_V00-NODE-MATRIX-001_TEST-V00-001_R01-R69资料覆盖矩阵.xlsx
+++ b/files/R01-R69全节点业务验收测试包/V00_R01-R69覆盖验证/V00_V00-NODE-MATRIX-001_TEST-V00-001_R01-R69资料覆盖矩阵.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="节点矩阵" sheetId="1" r:id="R9a577b432465495c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="节点矩阵" sheetId="1" r:id="R4a697afeeec04629"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -42,7 +42,7 @@
       <x:name val="Arial Unicode MS"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -59,8 +59,13 @@
         <x:fgColor rgb="FFFCE8E6"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3F1"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="9">
+  <x:borders count="17">
     <x:border/>
     <x:border>
       <x:left/>
@@ -90,11 +95,63 @@
       <x:right/>
       <x:bottom/>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="41">
+  <x:cellXfs count="69">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -186,6 +243,70 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -216,6 +337,38 @@
     </x:dxf>
   </x:dxfs>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="876300"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="f4aca723-a6ec-45ee-800a-2af0a5097197"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R45b1f554563d4737"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -417,6 +570,7 @@
     <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="18" hidden="0" customHeight="1">
@@ -426,14 +580,16 @@
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
       <x:c r="D1" s="4"/>
-    </x:row>
-    <x:row r="2" ht="21.600000381469727" hidden="0" customHeight="1">
+      <x:c r="E1" s="4"/>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="9" t="str">
         <x:v>测试专用／合成资料／不得用于真实工程｜TEST-ONLY / SYNTHETIC / NOT FOR REAL ENGINEERING USE｜文件编号：TEST-V00-001｜版本：0｜日期：2026-07-15</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
       <x:c r="D2" s="9"/>
+      <x:c r="E2" s="9"/>
     </x:row>
     <x:row r="3"/>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -730,7 +886,7 @@
         <x:v>已覆盖</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="15" hidden="0" customHeight="1">
+    <x:row r="25" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A25" s="35" t="str">
         <x:v>R21</x:v>
       </x:c>
@@ -738,7 +894,7 @@
         <x:v>资料节点</x:v>
       </x:c>
       <x:c r="C25" s="36" t="str">
-        <x:v>S01-DESIGN-001、S01-ACCEPT-001、S01-MARK-001</x:v>
+        <x:v>S01-DESIGN-001、S01-ACCEPT-001、S01-MARK-001、S01-PHOTO-001</x:v>
       </x:c>
       <x:c r="D25" s="37" t="str">
         <x:v>已覆盖</x:v>
@@ -780,7 +936,7 @@
         <x:v>资料节点</x:v>
       </x:c>
       <x:c r="C28" s="36" t="str">
-        <x:v>B00-WELD-001、S03-WELDER-001</x:v>
+        <x:v>B00-WELD-001、B00-QUERY-001、S03-WELDER-001</x:v>
       </x:c>
       <x:c r="D28" s="37" t="str">
         <x:v>已覆盖</x:v>
@@ -836,7 +992,7 @@
         <x:v>资料节点</x:v>
       </x:c>
       <x:c r="C32" s="36" t="str">
-        <x:v>B00-WELD-LEDGER-001</x:v>
+        <x:v>B00-WELD-LEDGER-001、B00-PHOTO-001</x:v>
       </x:c>
       <x:c r="D32" s="37" t="str">
         <x:v>已覆盖</x:v>
@@ -864,7 +1020,7 @@
         <x:v>资料节点</x:v>
       </x:c>
       <x:c r="C34" s="36" t="str">
-        <x:v>B00-WELD-LEDGER-001</x:v>
+        <x:v>B00-WELD-LEDGER-001、B00-PHOTO-002</x:v>
       </x:c>
       <x:c r="D34" s="37" t="str">
         <x:v>已覆盖</x:v>
@@ -1018,7 +1174,7 @@
         <x:v>资料节点</x:v>
       </x:c>
       <x:c r="C45" s="36" t="str">
-        <x:v>B00-INSTALL-001</x:v>
+        <x:v>B00-INSTALL-001、B00-FILM-001</x:v>
       </x:c>
       <x:c r="D45" s="37" t="str">
         <x:v>已覆盖</x:v>
@@ -1032,7 +1188,7 @@
         <x:v>资料节点</x:v>
       </x:c>
       <x:c r="C46" s="36" t="str">
-        <x:v>B00-INSTALL-001</x:v>
+        <x:v>B00-INSTALL-001、B00-PHOTO-003、B00-FILM-002</x:v>
       </x:c>
       <x:c r="D46" s="37" t="str">
         <x:v>已覆盖</x:v>
@@ -1060,7 +1216,7 @@
         <x:v>资料节点</x:v>
       </x:c>
       <x:c r="C48" s="36" t="str">
-        <x:v>B00-INSTALL-001</x:v>
+        <x:v>B00-INSTALL-001、B00-PHOTO-004</x:v>
       </x:c>
       <x:c r="D48" s="37" t="str">
         <x:v>已覆盖</x:v>
@@ -1130,7 +1286,7 @@
         <x:v>资料节点</x:v>
       </x:c>
       <x:c r="C53" s="36" t="str">
-        <x:v>S04-DESIGN-001、S04-DIAGRAM-001、S04-INSTALL-001、S04-PHOTO-001</x:v>
+        <x:v>S04-DESIGN-001、S04-DIAGRAM-001、S04-INSTALL-001、S04-PHOTO-002</x:v>
       </x:c>
       <x:c r="D53" s="37" t="str">
         <x:v>已覆盖</x:v>
@@ -1144,7 +1300,7 @@
         <x:v>资料节点</x:v>
       </x:c>
       <x:c r="C54" s="36" t="str">
-        <x:v>S04-DESIGN-001、S04-EQUIP-001、S04-INSTALL-001</x:v>
+        <x:v>S04-DESIGN-001、S04-EQUIP-001、S04-INSTALL-001、S04-PHOTO-003</x:v>
       </x:c>
       <x:c r="D54" s="37" t="str">
         <x:v>已覆盖</x:v>
@@ -1158,13 +1314,13 @@
         <x:v>资料节点</x:v>
       </x:c>
       <x:c r="C55" s="36" t="str">
-        <x:v>S04-DESIGN-001、S04-EQUIP-001、S04-INSTALL-001</x:v>
+        <x:v>S04-DESIGN-001、S04-EQUIP-001、S04-INSTALL-001、S04-PHOTO-004</x:v>
       </x:c>
       <x:c r="D55" s="37" t="str">
         <x:v>已覆盖</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="15" hidden="0" customHeight="1">
+    <x:row r="56" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A56" s="35" t="str">
         <x:v>R52</x:v>
       </x:c>
@@ -1172,7 +1328,7 @@
         <x:v>资料节点</x:v>
       </x:c>
       <x:c r="C56" s="36" t="str">
-        <x:v>S04-DESIGN-001、S04-INSTALL-001</x:v>
+        <x:v>S04-DESIGN-001、S04-INSTALL-001、S04-PHOTO-005</x:v>
       </x:c>
       <x:c r="D56" s="37" t="str">
         <x:v>已覆盖</x:v>
@@ -1186,7 +1342,7 @@
         <x:v>资料节点</x:v>
       </x:c>
       <x:c r="C57" s="36" t="str">
-        <x:v>S04-DESIGN-001、S04-DIAGRAM-001、S04-INSTALL-001、S04-PHOTO-001</x:v>
+        <x:v>S04-DESIGN-001、S04-DIAGRAM-001、S04-INSTALL-001、S04-PHOTO-006</x:v>
       </x:c>
       <x:c r="D57" s="37" t="str">
         <x:v>已覆盖</x:v>
@@ -1354,7 +1510,7 @@
         <x:v>资料节点</x:v>
       </x:c>
       <x:c r="C69" s="36" t="str">
-        <x:v>S06-APPROVAL-001、S06-NDT-001</x:v>
+        <x:v>S06-APPROVAL-001、S06-NDT-001、S06-FILM-001</x:v>
       </x:c>
       <x:c r="D69" s="37" t="str">
         <x:v>已覆盖</x:v>
@@ -1410,18 +1566,50 @@
         <x:v>工作流节点</x:v>
       </x:c>
       <x:c r="C73" s="39" t="str">
-        <x:v>无外部文件绑定</x:v>
+        <x:v>V00-R69-001</x:v>
       </x:c>
       <x:c r="D73" s="40" t="str">
         <x:v>已覆盖</x:v>
       </x:c>
     </x:row>
     <x:row r="74"/>
-    <x:row r="75"/>
+    <x:row r="75" ht="15" hidden="0" customHeight="1">
+      <x:c r="A75" s="60" t="str">
+        <x:v>电子签署（测试）｜资料验收测试专用章</x:v>
+      </x:c>
+      <x:c r="B75" s="61"/>
+      <x:c r="C75" s="61"/>
+      <x:c r="D75" s="61"/>
+      <x:c r="E75" s="62"/>
+    </x:row>
+    <x:row r="76" ht="15" hidden="0" customHeight="1">
+      <x:c r="A76" s="63"/>
+      <x:c r="B76" s="64"/>
+      <x:c r="C76" s="64"/>
+      <x:c r="D76" s="64"/>
+      <x:c r="E76" s="65"/>
+    </x:row>
+    <x:row r="77" ht="15" hidden="0" customHeight="1">
+      <x:c r="A77" s="63"/>
+      <x:c r="B77" s="64"/>
+      <x:c r="C77" s="64"/>
+      <x:c r="D77" s="64"/>
+      <x:c r="E77" s="65"/>
+    </x:row>
+    <x:row r="78" ht="15" hidden="0" customHeight="1">
+      <x:c r="A78" s="66"/>
+      <x:c r="B78" s="67"/>
+      <x:c r="C78" s="67"/>
+      <x:c r="D78" s="67"/>
+      <x:c r="E78" s="68"/>
+    </x:row>
+    <x:row r="79"/>
+    <x:row r="80"/>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:D1"/>
-    <x:mergeCell ref="A2:D2"/>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A75:C75"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A5:D73">
     <x:cfRule type="expression" dxfId="0" priority="1">
@@ -1432,5 +1620,6 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5722b3a1403f4a38"/>
 </x:worksheet>
 </file>